--- a/outputs/test51_report.xlsx
+++ b/outputs/test51_report.xlsx
@@ -3,12 +3,21 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Summary" sheetId="1" r:id="rId1"/>
-    <sheet name="Events" sheetId="2" r:id="rId2"/>
-    <sheet name="Parameters" sheetId="3" r:id="rId3"/>
-    <sheet name="OperationalDefinitions" sheetId="4" r:id="rId4"/>
-    <sheet name="Provenance" sheetId="5" r:id="rId5"/>
+    <sheet name="Results" sheetId="1" r:id="rId1"/>
+    <sheet name="Summary" sheetId="2" r:id="rId2"/>
+    <sheet name="Events" sheetId="3" r:id="rId3"/>
+    <sheet name="Parameters" sheetId="4" r:id="rId4"/>
+    <sheet name="OperationalDefinitions" sheetId="5" r:id="rId5"/>
+    <sheet name="Provenance" sheetId="6" r:id="rId6"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Results'!A1:Z2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1">'Summary'!A1:EV2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2">'Events'!A1:X12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3">'Parameters'!A1:C42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4">'OperationalDefinitions'!A1:F17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5">'Provenance'!A1:U2</definedName>
+  </definedNames>
 </workbook>
 </file>
 
@@ -401,7 +410,361 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z2"/>
+  <cols>
+    <col min="1" max="1" width="18.83203125" customWidth="1"/>
+    <col min="2" max="2" width="12.83203125" customWidth="1"/>
+    <col min="3" max="3" width="14.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" customWidth="1"/>
+    <col min="5" max="5" width="10.83203125" customWidth="1"/>
+    <col min="6" max="6" width="12.83203125" customWidth="1"/>
+    <col min="7" max="7" width="28.83203125" customWidth="1"/>
+    <col min="8" max="8" width="44.83203125" customWidth="1"/>
+    <col min="9" max="9" width="18.83203125" customWidth="1"/>
+    <col min="10" max="10" width="16.83203125" customWidth="1"/>
+    <col min="11" max="11" width="16.83203125" customWidth="1"/>
+    <col min="12" max="12" width="16.83203125" customWidth="1"/>
+    <col min="13" max="13" width="16.83203125" customWidth="1"/>
+    <col min="14" max="14" width="14.83203125" customWidth="1"/>
+    <col min="15" max="15" width="14.83203125" customWidth="1"/>
+    <col min="16" max="16" width="14.83203125" customWidth="1"/>
+    <col min="17" max="17" width="14.83203125" customWidth="1"/>
+    <col min="18" max="18" width="14.83203125" customWidth="1"/>
+    <col min="19" max="19" width="12.83203125" customWidth="1"/>
+    <col min="20" max="20" width="12.83203125" customWidth="1"/>
+    <col min="21" max="21" width="18.83203125" customWidth="1"/>
+    <col min="22" max="22" width="18.83203125" customWidth="1"/>
+    <col min="23" max="23" width="18.83203125" customWidth="1"/>
+    <col min="24" max="24" width="18.83203125" customWidth="1"/>
+    <col min="25" max="25" width="14.83203125" customWidth="1"/>
+    <col min="26" max="26" width="16.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>fileName</v>
+      </c>
+      <c r="B1" t="str">
+        <v>label</v>
+      </c>
+      <c r="C1" t="str">
+        <v>measurementBasis</v>
+      </c>
+      <c r="D1" t="str">
+        <v>targetStatus</v>
+      </c>
+      <c r="E1" t="str">
+        <v>targetHole</v>
+      </c>
+      <c r="F1" t="str">
+        <v>scaleStatus</v>
+      </c>
+      <c r="G1" t="str">
+        <v>physicalScale</v>
+      </c>
+      <c r="H1" t="str">
+        <v>escapeState</v>
+      </c>
+      <c r="I1" t="str">
+        <v>eventsReviewStatus</v>
+      </c>
+      <c r="J1" t="str">
+        <v>primaryLatency</v>
+      </c>
+      <c r="K1" t="str">
+        <v>totalLatency</v>
+      </c>
+      <c r="L1" t="str">
+        <v>primaryErrors</v>
+      </c>
+      <c r="M1" t="str">
+        <v>totalErrors</v>
+      </c>
+      <c r="N1" t="str">
+        <v>primaryErrorsConfirmedCount</v>
+      </c>
+      <c r="O1" t="str">
+        <v>primaryErrorsProvisionalCount</v>
+      </c>
+      <c r="P1" t="str">
+        <v>totalErrorsConfirmedCount</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>totalErrorsProvisionalCount</v>
+      </c>
+      <c r="R1" t="str">
+        <v>pathLength</v>
+      </c>
+      <c r="S1" t="str">
+        <v>meanSpeed</v>
+      </c>
+      <c r="T1" t="str">
+        <v>maxSpeed</v>
+      </c>
+      <c r="U1" t="str">
+        <v>meanSpeedDiagnostic</v>
+      </c>
+      <c r="V1" t="str">
+        <v>maxSpeedDiagnostic</v>
+      </c>
+      <c r="W1" t="str">
+        <v>targetQuadrantFraction</v>
+      </c>
+      <c r="X1" t="str">
+        <v>targetQuadrantTime</v>
+      </c>
+      <c r="Y1" t="str">
+        <v>searchStrategy</v>
+      </c>
+      <c r="Z1" t="str">
+        <v>searchStrategyOverride</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>test51.mp4</v>
+      </c>
+      <c r="B2" t="str">
+        <v>test51</v>
+      </c>
+      <c r="C2" t="str">
+        <v>corrected</v>
+      </c>
+      <c r="D2" t="str">
+        <v>unknown</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="F2" t="str">
+        <v>unknown</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Unknown (coordinates in px)</v>
+      </c>
+      <c r="H2" t="str">
+        <v>Candidate hole entry — not confirmed escape through protocol target — follow-up lower bound ≥ 44.244200 s</v>
+      </c>
+      <c r="I2" t="str">
+        <v>Current</v>
+      </c>
+      <c r="J2" t="str">
+        <v>Unavailable (Target hole not confirmed.)</v>
+      </c>
+      <c r="K2" t="str">
+        <v>Censored ≥ 44.24 s [escape_entry_uncertain]</v>
+      </c>
+      <c r="L2" t="str">
+        <v>Unavailable (Target hole not confirmed.)</v>
+      </c>
+      <c r="M2" t="str">
+        <v>Unavailable (Target hole not confirmed.)</v>
+      </c>
+      <c r="N2" t="str">
+        <v>Target hole not confirmed.</v>
+      </c>
+      <c r="O2" t="str">
+        <v>Target hole not confirmed.</v>
+      </c>
+      <c r="P2" t="str">
+        <v>Target hole not confirmed.</v>
+      </c>
+      <c r="Q2" t="str">
+        <v>Target hole not confirmed.</v>
+      </c>
+      <c r="R2" t="str">
+        <v>905.72 px</v>
+      </c>
+      <c r="S2" t="str">
+        <v>20.21 px/s</v>
+      </c>
+      <c r="T2" t="str">
+        <v>129.76 px/s</v>
+      </c>
+      <c r="U2" t="str">
+        <v>20.30 px/s</v>
+      </c>
+      <c r="V2" t="str">
+        <v>36567.67 px/s</v>
+      </c>
+      <c r="W2" t="str">
+        <v>Unavailable (Target hole not confirmed.)</v>
+      </c>
+      <c r="X2" t="str">
+        <v>Unavailable (Target hole not confirmed.)</v>
+      </c>
+      <c r="Y2" t="str">
+        <v>random</v>
+      </c>
+      <c r="Z2" t="str">
+        <v>—</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:Z2"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:Z2"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:EV2"/>
+  <cols>
+    <col min="1" max="1" width="14.83203125" customWidth="1"/>
+    <col min="2" max="2" width="14.83203125" customWidth="1"/>
+    <col min="3" max="3" width="14.83203125" customWidth="1"/>
+    <col min="4" max="4" width="14.83203125" customWidth="1"/>
+    <col min="5" max="5" width="14.83203125" customWidth="1"/>
+    <col min="6" max="6" width="14.83203125" customWidth="1"/>
+    <col min="7" max="7" width="14.83203125" customWidth="1"/>
+    <col min="8" max="8" width="14.83203125" customWidth="1"/>
+    <col min="9" max="9" width="14.83203125" customWidth="1"/>
+    <col min="10" max="10" width="14.83203125" customWidth="1"/>
+    <col min="11" max="11" width="14.83203125" customWidth="1"/>
+    <col min="12" max="12" width="14.83203125" customWidth="1"/>
+    <col min="13" max="13" width="14.83203125" customWidth="1"/>
+    <col min="14" max="14" width="14.83203125" customWidth="1"/>
+    <col min="15" max="15" width="14.83203125" customWidth="1"/>
+    <col min="16" max="16" width="14.83203125" customWidth="1"/>
+    <col min="17" max="17" width="14.83203125" customWidth="1"/>
+    <col min="18" max="18" width="14.83203125" customWidth="1"/>
+    <col min="19" max="19" width="14.83203125" customWidth="1"/>
+    <col min="20" max="20" width="14.83203125" customWidth="1"/>
+    <col min="21" max="21" width="14.83203125" customWidth="1"/>
+    <col min="22" max="22" width="14.83203125" customWidth="1"/>
+    <col min="23" max="23" width="14.83203125" customWidth="1"/>
+    <col min="24" max="24" width="14.83203125" customWidth="1"/>
+    <col min="25" max="25" width="14.83203125" customWidth="1"/>
+    <col min="26" max="26" width="14.83203125" customWidth="1"/>
+    <col min="27" max="27" width="14.83203125" customWidth="1"/>
+    <col min="28" max="28" width="14.83203125" customWidth="1"/>
+    <col min="29" max="29" width="14.83203125" customWidth="1"/>
+    <col min="30" max="30" width="14.83203125" customWidth="1"/>
+    <col min="31" max="31" width="14.83203125" customWidth="1"/>
+    <col min="32" max="32" width="14.83203125" customWidth="1"/>
+    <col min="33" max="33" width="14.83203125" customWidth="1"/>
+    <col min="34" max="34" width="14.83203125" customWidth="1"/>
+    <col min="35" max="35" width="14.83203125" customWidth="1"/>
+    <col min="36" max="36" width="14.83203125" customWidth="1"/>
+    <col min="37" max="37" width="14.83203125" customWidth="1"/>
+    <col min="38" max="38" width="14.83203125" customWidth="1"/>
+    <col min="39" max="39" width="14.83203125" customWidth="1"/>
+    <col min="40" max="40" width="14.83203125" customWidth="1"/>
+    <col min="41" max="41" width="14.83203125" customWidth="1"/>
+    <col min="42" max="42" width="14.83203125" customWidth="1"/>
+    <col min="43" max="43" width="14.83203125" customWidth="1"/>
+    <col min="44" max="44" width="14.83203125" customWidth="1"/>
+    <col min="45" max="45" width="14.83203125" customWidth="1"/>
+    <col min="46" max="46" width="14.83203125" customWidth="1"/>
+    <col min="47" max="47" width="14.83203125" customWidth="1"/>
+    <col min="48" max="48" width="14.83203125" customWidth="1"/>
+    <col min="49" max="49" width="14.83203125" customWidth="1"/>
+    <col min="50" max="50" width="14.83203125" customWidth="1"/>
+    <col min="51" max="51" width="14.83203125" customWidth="1"/>
+    <col min="52" max="52" width="14.83203125" customWidth="1"/>
+    <col min="53" max="53" width="14.83203125" customWidth="1"/>
+    <col min="54" max="54" width="14.83203125" customWidth="1"/>
+    <col min="55" max="55" width="14.83203125" customWidth="1"/>
+    <col min="56" max="56" width="14.83203125" customWidth="1"/>
+    <col min="57" max="57" width="14.83203125" customWidth="1"/>
+    <col min="58" max="58" width="14.83203125" customWidth="1"/>
+    <col min="59" max="59" width="14.83203125" customWidth="1"/>
+    <col min="60" max="60" width="14.83203125" customWidth="1"/>
+    <col min="61" max="61" width="14.83203125" customWidth="1"/>
+    <col min="62" max="62" width="14.83203125" customWidth="1"/>
+    <col min="63" max="63" width="14.83203125" customWidth="1"/>
+    <col min="64" max="64" width="14.83203125" customWidth="1"/>
+    <col min="65" max="65" width="14.83203125" customWidth="1"/>
+    <col min="66" max="66" width="14.83203125" customWidth="1"/>
+    <col min="67" max="67" width="14.83203125" customWidth="1"/>
+    <col min="68" max="68" width="14.83203125" customWidth="1"/>
+    <col min="69" max="69" width="14.83203125" customWidth="1"/>
+    <col min="70" max="70" width="14.83203125" customWidth="1"/>
+    <col min="71" max="71" width="14.83203125" customWidth="1"/>
+    <col min="72" max="72" width="14.83203125" customWidth="1"/>
+    <col min="73" max="73" width="14.83203125" customWidth="1"/>
+    <col min="74" max="74" width="14.83203125" customWidth="1"/>
+    <col min="75" max="75" width="14.83203125" customWidth="1"/>
+    <col min="76" max="76" width="14.83203125" customWidth="1"/>
+    <col min="77" max="77" width="14.83203125" customWidth="1"/>
+    <col min="78" max="78" width="14.83203125" customWidth="1"/>
+    <col min="79" max="79" width="14.83203125" customWidth="1"/>
+    <col min="80" max="80" width="14.83203125" customWidth="1"/>
+    <col min="81" max="81" width="14.83203125" customWidth="1"/>
+    <col min="82" max="82" width="14.83203125" customWidth="1"/>
+    <col min="83" max="83" width="14.83203125" customWidth="1"/>
+    <col min="84" max="84" width="14.83203125" customWidth="1"/>
+    <col min="85" max="85" width="14.83203125" customWidth="1"/>
+    <col min="86" max="86" width="14.83203125" customWidth="1"/>
+    <col min="87" max="87" width="14.83203125" customWidth="1"/>
+    <col min="88" max="88" width="14.83203125" customWidth="1"/>
+    <col min="89" max="89" width="14.83203125" customWidth="1"/>
+    <col min="90" max="90" width="14.83203125" customWidth="1"/>
+    <col min="91" max="91" width="14.83203125" customWidth="1"/>
+    <col min="92" max="92" width="14.83203125" customWidth="1"/>
+    <col min="93" max="93" width="14.83203125" customWidth="1"/>
+    <col min="94" max="94" width="14.83203125" customWidth="1"/>
+    <col min="95" max="95" width="14.83203125" customWidth="1"/>
+    <col min="96" max="96" width="14.83203125" customWidth="1"/>
+    <col min="97" max="97" width="14.83203125" customWidth="1"/>
+    <col min="98" max="98" width="14.83203125" customWidth="1"/>
+    <col min="99" max="99" width="14.83203125" customWidth="1"/>
+    <col min="100" max="100" width="14.83203125" customWidth="1"/>
+    <col min="101" max="101" width="14.83203125" customWidth="1"/>
+    <col min="102" max="102" width="14.83203125" customWidth="1"/>
+    <col min="103" max="103" width="14.83203125" customWidth="1"/>
+    <col min="104" max="104" width="14.83203125" customWidth="1"/>
+    <col min="105" max="105" width="14.83203125" customWidth="1"/>
+    <col min="106" max="106" width="14.83203125" customWidth="1"/>
+    <col min="107" max="107" width="14.83203125" customWidth="1"/>
+    <col min="108" max="108" width="14.83203125" customWidth="1"/>
+    <col min="109" max="109" width="14.83203125" customWidth="1"/>
+    <col min="110" max="110" width="14.83203125" customWidth="1"/>
+    <col min="111" max="111" width="14.83203125" customWidth="1"/>
+    <col min="112" max="112" width="14.83203125" customWidth="1"/>
+    <col min="113" max="113" width="14.83203125" customWidth="1"/>
+    <col min="114" max="114" width="14.83203125" customWidth="1"/>
+    <col min="115" max="115" width="14.83203125" customWidth="1"/>
+    <col min="116" max="116" width="14.83203125" customWidth="1"/>
+    <col min="117" max="117" width="14.83203125" customWidth="1"/>
+    <col min="118" max="118" width="14.83203125" customWidth="1"/>
+    <col min="119" max="119" width="14.83203125" customWidth="1"/>
+    <col min="120" max="120" width="14.83203125" customWidth="1"/>
+    <col min="121" max="121" width="14.83203125" customWidth="1"/>
+    <col min="122" max="122" width="14.83203125" customWidth="1"/>
+    <col min="123" max="123" width="14.83203125" customWidth="1"/>
+    <col min="124" max="124" width="14.83203125" customWidth="1"/>
+    <col min="125" max="125" width="14.83203125" customWidth="1"/>
+    <col min="126" max="126" width="14.83203125" customWidth="1"/>
+    <col min="127" max="127" width="14.83203125" customWidth="1"/>
+    <col min="128" max="128" width="14.83203125" customWidth="1"/>
+    <col min="129" max="129" width="14.83203125" customWidth="1"/>
+    <col min="130" max="130" width="14.83203125" customWidth="1"/>
+    <col min="131" max="131" width="14.83203125" customWidth="1"/>
+    <col min="132" max="132" width="14.83203125" customWidth="1"/>
+    <col min="133" max="133" width="14.83203125" customWidth="1"/>
+    <col min="134" max="134" width="14.83203125" customWidth="1"/>
+    <col min="135" max="135" width="14.83203125" customWidth="1"/>
+    <col min="136" max="136" width="14.83203125" customWidth="1"/>
+    <col min="137" max="137" width="14.83203125" customWidth="1"/>
+    <col min="138" max="138" width="14.83203125" customWidth="1"/>
+    <col min="139" max="139" width="14.83203125" customWidth="1"/>
+    <col min="140" max="140" width="14.83203125" customWidth="1"/>
+    <col min="141" max="141" width="14.83203125" customWidth="1"/>
+    <col min="142" max="142" width="14.83203125" customWidth="1"/>
+    <col min="143" max="143" width="14.83203125" customWidth="1"/>
+    <col min="144" max="144" width="14.83203125" customWidth="1"/>
+    <col min="145" max="145" width="14.83203125" customWidth="1"/>
+    <col min="146" max="146" width="14.83203125" customWidth="1"/>
+    <col min="147" max="147" width="14.83203125" customWidth="1"/>
+    <col min="148" max="148" width="14.83203125" customWidth="1"/>
+    <col min="149" max="149" width="14.83203125" customWidth="1"/>
+    <col min="150" max="150" width="14.83203125" customWidth="1"/>
+    <col min="151" max="151" width="14.83203125" customWidth="1"/>
+    <col min="152" max="152" width="14.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -896,7 +1259,7 @@
         <v>2026-09-07T18:12:35.996Z</v>
       </c>
       <c r="P2" t="str">
-        <v>2026-09-07T19:54:09.009Z</v>
+        <v>2026-09-07T20:08:18.625Z</v>
       </c>
       <c r="Q2" t="str">
         <v>false</v>
@@ -907,18 +1270,6 @@
       <c r="T2" t="str">
         <v>random</v>
       </c>
-      <c r="V2">
-        <v>0</v>
-      </c>
-      <c r="W2">
-        <v>0</v>
-      </c>
-      <c r="X2">
-        <v>0</v>
-      </c>
-      <c r="Y2">
-        <v>0</v>
-      </c>
       <c r="AA2" t="str">
         <v>unavailable</v>
       </c>
@@ -1164,129 +1515,118 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:EV2"/>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:EV2"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:X12"/>
+  <cols>
+    <col min="1" max="1" width="14.83203125" customWidth="1"/>
+    <col min="2" max="2" width="36.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+    <col min="4" max="4" width="28.83203125" customWidth="1"/>
+    <col min="5" max="5" width="10.83203125" customWidth="1"/>
+    <col min="6" max="6" width="12.83203125" customWidth="1"/>
+    <col min="7" max="7" width="18.83203125" customWidth="1"/>
+    <col min="8" max="8" width="18.83203125" customWidth="1"/>
+    <col min="9" max="9" width="18.83203125" customWidth="1"/>
+    <col min="10" max="10" width="18.83203125" customWidth="1"/>
+    <col min="11" max="11" width="16.83203125" customWidth="1"/>
+    <col min="12" max="12" width="16.83203125" customWidth="1"/>
+    <col min="13" max="13" width="16.83203125" customWidth="1"/>
+    <col min="14" max="14" width="10.83203125" customWidth="1"/>
+    <col min="15" max="15" width="12.83203125" customWidth="1"/>
+    <col min="16" max="16" width="12.83203125" customWidth="1"/>
+    <col min="17" max="17" width="10.83203125" customWidth="1"/>
+    <col min="18" max="18" width="10.83203125" customWidth="1"/>
+    <col min="19" max="19" width="14.83203125" customWidth="1"/>
+    <col min="20" max="20" width="14.83203125" customWidth="1"/>
+    <col min="21" max="21" width="18.83203125" customWidth="1"/>
+    <col min="22" max="22" width="24.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>trialId</v>
-      </c>
-      <c r="B1" t="str">
-        <v>eventId</v>
-      </c>
-      <c r="C1" t="str">
-        <v>type</v>
-      </c>
-      <c r="D1" t="str">
-        <v>exportLabel</v>
-      </c>
-      <c r="E1" t="str">
-        <v>holeDisplay</v>
-      </c>
-      <c r="F1" t="str">
-        <v>holeIdInternal</v>
-      </c>
-      <c r="G1" t="str">
-        <v>startFrameIndex</v>
-      </c>
-      <c r="H1" t="str">
-        <v>endFrameIndex</v>
-      </c>
-      <c r="I1" t="str">
-        <v>startTimeSec</v>
-      </c>
-      <c r="J1" t="str">
-        <v>endTimeSec</v>
-      </c>
-      <c r="K1" t="str">
-        <v>entryOnsetTimeSec</v>
-      </c>
-      <c r="L1" t="str">
-        <v>completionTimeSec</v>
-      </c>
-      <c r="M1" t="str">
-        <v>censorBoundaryTimeSec</v>
-      </c>
-      <c r="N1" t="str">
-        <v>origin</v>
-      </c>
-      <c r="O1" t="str">
-        <v>status</v>
-      </c>
-      <c r="P1" t="str">
-        <v>confidence</v>
-      </c>
-      <c r="Q1" t="str">
-        <v>visitIndex</v>
-      </c>
-      <c r="R1" t="str">
-        <v>isRevisit</v>
-      </c>
-      <c r="S1" t="str">
-        <v>bodyEntryPath</v>
-      </c>
-      <c r="T1" t="str">
-        <v>bodyEntryVersion</v>
-      </c>
-      <c r="U1" t="str">
-        <v>pixelEvidenceComplete</v>
-      </c>
-      <c r="V1" t="str">
-        <v>notes</v>
+        <v>Frame indices: startFrameIndex and endFrameIndex are 0-based internal decoder indices. startFrameDisplay and endFrameDisplay add 1 for human-readable frame numbers.</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>e31e497a-d9c4-4ec0-b47f-531e3e5f83d8</v>
+        <v>trialId</v>
       </c>
       <c r="B2" t="str">
-        <v>ad3cf284-3df5-48bb-9622-4c7408cfe464</v>
+        <v>eventId</v>
       </c>
       <c r="C2" t="str">
-        <v>investigation</v>
+        <v>type</v>
       </c>
       <c r="D2" t="str">
-        <v>investigation</v>
-      </c>
-      <c r="E2">
-        <v>11</v>
-      </c>
-      <c r="F2">
-        <v>10</v>
-      </c>
-      <c r="G2">
-        <v>86</v>
-      </c>
-      <c r="H2">
-        <v>122</v>
-      </c>
-      <c r="I2">
-        <v>5.872533</v>
-      </c>
-      <c r="J2">
-        <v>8.274933</v>
+        <v>exportLabel</v>
+      </c>
+      <c r="E2" t="str">
+        <v>holeDisplay</v>
+      </c>
+      <c r="F2" t="str">
+        <v>holeIdInternal</v>
+      </c>
+      <c r="G2" t="str">
+        <v>startFrameIndex</v>
+      </c>
+      <c r="H2" t="str">
+        <v>endFrameIndex</v>
+      </c>
+      <c r="I2" t="str">
+        <v>startFrameDisplay</v>
+      </c>
+      <c r="J2" t="str">
+        <v>endFrameDisplay</v>
+      </c>
+      <c r="K2" t="str">
+        <v>startTimeSec</v>
+      </c>
+      <c r="L2" t="str">
+        <v>endTimeSec</v>
+      </c>
+      <c r="M2" t="str">
+        <v>entryOnsetTimeSec</v>
       </c>
       <c r="N2" t="str">
-        <v>auto</v>
+        <v>completionTimeSec</v>
       </c>
       <c r="O2" t="str">
-        <v>proposed</v>
+        <v>censorBoundaryTimeSec</v>
       </c>
       <c r="P2" t="str">
-        <v>medium</v>
-      </c>
-      <c r="Q2">
-        <v>1</v>
+        <v>origin</v>
+      </c>
+      <c r="Q2" t="str">
+        <v>status</v>
       </c>
       <c r="R2" t="str">
-        <v>false</v>
+        <v>confidence</v>
+      </c>
+      <c r="S2" t="str">
+        <v>visitIndex</v>
+      </c>
+      <c r="T2" t="str">
+        <v>isRevisit</v>
+      </c>
+      <c r="U2" t="str">
+        <v>bodyEntryPath</v>
+      </c>
+      <c r="V2" t="str">
+        <v>bodyEntryVersion</v>
+      </c>
+      <c r="W2" t="str">
+        <v>pixelEvidenceComplete</v>
+      </c>
+      <c r="X2" t="str">
+        <v>notes</v>
       </c>
     </row>
     <row r="3">
@@ -1294,7 +1634,7 @@
         <v>e31e497a-d9c4-4ec0-b47f-531e3e5f83d8</v>
       </c>
       <c r="B3" t="str">
-        <v>a3fc2f00-f373-41ed-80b4-975d191ae2ff</v>
+        <v>ad3cf284-3df5-48bb-9622-4c7408cfe464</v>
       </c>
       <c r="C3" t="str">
         <v>investigation</v>
@@ -1303,36 +1643,42 @@
         <v>investigation</v>
       </c>
       <c r="E3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G3">
-        <v>136</v>
+        <v>86</v>
       </c>
       <c r="H3">
-        <v>178</v>
+        <v>122</v>
       </c>
       <c r="I3">
-        <v>9.2092</v>
+        <v>87</v>
       </c>
       <c r="J3">
-        <v>12.012</v>
-      </c>
-      <c r="N3" t="str">
+        <v>123</v>
+      </c>
+      <c r="K3">
+        <v>5.872533</v>
+      </c>
+      <c r="L3">
+        <v>8.274933</v>
+      </c>
+      <c r="P3" t="str">
         <v>auto</v>
       </c>
-      <c r="O3" t="str">
+      <c r="Q3" t="str">
         <v>proposed</v>
       </c>
-      <c r="P3" t="str">
+      <c r="R3" t="str">
         <v>medium</v>
       </c>
-      <c r="Q3">
+      <c r="S3">
         <v>1</v>
       </c>
-      <c r="R3" t="str">
+      <c r="T3" t="str">
         <v>false</v>
       </c>
     </row>
@@ -1341,7 +1687,7 @@
         <v>e31e497a-d9c4-4ec0-b47f-531e3e5f83d8</v>
       </c>
       <c r="B4" t="str">
-        <v>b812c2e2-e459-4a2a-82b8-3bdbeb368dab</v>
+        <v>a3fc2f00-f373-41ed-80b4-975d191ae2ff</v>
       </c>
       <c r="C4" t="str">
         <v>investigation</v>
@@ -1350,37 +1696,43 @@
         <v>investigation</v>
       </c>
       <c r="E4">
+        <v>12</v>
+      </c>
+      <c r="F4">
         <v>11</v>
       </c>
-      <c r="F4">
-        <v>10</v>
-      </c>
       <c r="G4">
-        <v>194</v>
+        <v>136</v>
       </c>
       <c r="H4">
-        <v>345</v>
+        <v>178</v>
       </c>
       <c r="I4">
-        <v>13.079733</v>
+        <v>137</v>
       </c>
       <c r="J4">
-        <v>23.156467</v>
-      </c>
-      <c r="N4" t="str">
+        <v>179</v>
+      </c>
+      <c r="K4">
+        <v>9.2092</v>
+      </c>
+      <c r="L4">
+        <v>12.012</v>
+      </c>
+      <c r="P4" t="str">
         <v>auto</v>
       </c>
-      <c r="O4" t="str">
+      <c r="Q4" t="str">
         <v>proposed</v>
       </c>
-      <c r="P4" t="str">
+      <c r="R4" t="str">
         <v>medium</v>
       </c>
-      <c r="Q4">
-        <v>2</v>
-      </c>
-      <c r="R4" t="str">
-        <v>true</v>
+      <c r="S4">
+        <v>1</v>
+      </c>
+      <c r="T4" t="str">
+        <v>false</v>
       </c>
     </row>
     <row r="5">
@@ -1388,7 +1740,7 @@
         <v>e31e497a-d9c4-4ec0-b47f-531e3e5f83d8</v>
       </c>
       <c r="B5" t="str">
-        <v>d1beac6e-ec45-4cf3-8ec3-73ce19d00f60</v>
+        <v>b812c2e2-e459-4a2a-82b8-3bdbeb368dab</v>
       </c>
       <c r="C5" t="str">
         <v>investigation</v>
@@ -1403,30 +1755,36 @@
         <v>10</v>
       </c>
       <c r="G5">
-        <v>350</v>
+        <v>194</v>
       </c>
       <c r="H5">
-        <v>358</v>
+        <v>345</v>
       </c>
       <c r="I5">
-        <v>23.490133</v>
+        <v>195</v>
       </c>
       <c r="J5">
-        <v>24.024</v>
-      </c>
-      <c r="N5" t="str">
+        <v>346</v>
+      </c>
+      <c r="K5">
+        <v>13.079733</v>
+      </c>
+      <c r="L5">
+        <v>23.156467</v>
+      </c>
+      <c r="P5" t="str">
         <v>auto</v>
       </c>
-      <c r="O5" t="str">
+      <c r="Q5" t="str">
         <v>proposed</v>
       </c>
-      <c r="P5" t="str">
+      <c r="R5" t="str">
         <v>medium</v>
       </c>
-      <c r="Q5">
-        <v>3</v>
-      </c>
-      <c r="R5" t="str">
+      <c r="S5">
+        <v>2</v>
+      </c>
+      <c r="T5" t="str">
         <v>true</v>
       </c>
     </row>
@@ -1435,7 +1793,7 @@
         <v>e31e497a-d9c4-4ec0-b47f-531e3e5f83d8</v>
       </c>
       <c r="B6" t="str">
-        <v>612ae6cc-d804-4146-9b2d-190c000b258a</v>
+        <v>d1beac6e-ec45-4cf3-8ec3-73ce19d00f60</v>
       </c>
       <c r="C6" t="str">
         <v>investigation</v>
@@ -1444,37 +1802,43 @@
         <v>investigation</v>
       </c>
       <c r="E6">
+        <v>11</v>
+      </c>
+      <c r="F6">
         <v>10</v>
       </c>
-      <c r="F6">
-        <v>9</v>
-      </c>
       <c r="G6">
-        <v>361</v>
+        <v>350</v>
       </c>
       <c r="H6">
-        <v>393</v>
+        <v>358</v>
       </c>
       <c r="I6">
-        <v>24.2242</v>
+        <v>351</v>
       </c>
       <c r="J6">
-        <v>26.359667</v>
-      </c>
-      <c r="N6" t="str">
+        <v>359</v>
+      </c>
+      <c r="K6">
+        <v>23.490133</v>
+      </c>
+      <c r="L6">
+        <v>24.024</v>
+      </c>
+      <c r="P6" t="str">
         <v>auto</v>
       </c>
-      <c r="O6" t="str">
+      <c r="Q6" t="str">
         <v>proposed</v>
       </c>
-      <c r="P6" t="str">
+      <c r="R6" t="str">
         <v>medium</v>
       </c>
-      <c r="Q6">
-        <v>1</v>
-      </c>
-      <c r="R6" t="str">
-        <v>false</v>
+      <c r="S6">
+        <v>3</v>
+      </c>
+      <c r="T6" t="str">
+        <v>true</v>
       </c>
     </row>
     <row r="7">
@@ -1482,7 +1846,7 @@
         <v>e31e497a-d9c4-4ec0-b47f-531e3e5f83d8</v>
       </c>
       <c r="B7" t="str">
-        <v>b897b531-67ae-4912-9f69-5abd0f375e30</v>
+        <v>612ae6cc-d804-4146-9b2d-190c000b258a</v>
       </c>
       <c r="C7" t="str">
         <v>investigation</v>
@@ -1497,31 +1861,37 @@
         <v>9</v>
       </c>
       <c r="G7">
-        <v>398</v>
+        <v>361</v>
       </c>
       <c r="H7">
-        <v>408</v>
+        <v>393</v>
       </c>
       <c r="I7">
-        <v>26.693333</v>
+        <v>362</v>
       </c>
       <c r="J7">
-        <v>27.360667</v>
-      </c>
-      <c r="N7" t="str">
+        <v>394</v>
+      </c>
+      <c r="K7">
+        <v>24.2242</v>
+      </c>
+      <c r="L7">
+        <v>26.359667</v>
+      </c>
+      <c r="P7" t="str">
         <v>auto</v>
       </c>
-      <c r="O7" t="str">
+      <c r="Q7" t="str">
         <v>proposed</v>
       </c>
-      <c r="P7" t="str">
+      <c r="R7" t="str">
         <v>medium</v>
       </c>
-      <c r="Q7">
-        <v>2</v>
-      </c>
-      <c r="R7" t="str">
-        <v>true</v>
+      <c r="S7">
+        <v>1</v>
+      </c>
+      <c r="T7" t="str">
+        <v>false</v>
       </c>
     </row>
     <row r="8">
@@ -1529,7 +1899,7 @@
         <v>e31e497a-d9c4-4ec0-b47f-531e3e5f83d8</v>
       </c>
       <c r="B8" t="str">
-        <v>15259281-2cd9-4c73-8bc2-4e5ecce5237c</v>
+        <v>b897b531-67ae-4912-9f69-5abd0f375e30</v>
       </c>
       <c r="C8" t="str">
         <v>investigation</v>
@@ -1538,37 +1908,43 @@
         <v>investigation</v>
       </c>
       <c r="E8">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F8">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="G8">
-        <v>501</v>
+        <v>398</v>
       </c>
       <c r="H8">
-        <v>526</v>
+        <v>408</v>
       </c>
       <c r="I8">
-        <v>33.566867</v>
+        <v>399</v>
       </c>
       <c r="J8">
-        <v>35.2352</v>
-      </c>
-      <c r="N8" t="str">
+        <v>409</v>
+      </c>
+      <c r="K8">
+        <v>26.693333</v>
+      </c>
+      <c r="L8">
+        <v>27.360667</v>
+      </c>
+      <c r="P8" t="str">
         <v>auto</v>
       </c>
-      <c r="O8" t="str">
+      <c r="Q8" t="str">
         <v>proposed</v>
       </c>
-      <c r="P8" t="str">
+      <c r="R8" t="str">
         <v>medium</v>
       </c>
-      <c r="Q8">
-        <v>1</v>
-      </c>
-      <c r="R8" t="str">
-        <v>false</v>
+      <c r="S8">
+        <v>2</v>
+      </c>
+      <c r="T8" t="str">
+        <v>true</v>
       </c>
     </row>
     <row r="9">
@@ -1576,7 +1952,7 @@
         <v>e31e497a-d9c4-4ec0-b47f-531e3e5f83d8</v>
       </c>
       <c r="B9" t="str">
-        <v>43016980-1892-4da4-a53e-5905bf8ef55f</v>
+        <v>15259281-2cd9-4c73-8bc2-4e5ecce5237c</v>
       </c>
       <c r="C9" t="str">
         <v>investigation</v>
@@ -1585,36 +1961,42 @@
         <v>investigation</v>
       </c>
       <c r="E9">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G9">
-        <v>537</v>
+        <v>501</v>
       </c>
       <c r="H9">
-        <v>559</v>
+        <v>526</v>
       </c>
       <c r="I9">
-        <v>35.969267</v>
+        <v>502</v>
       </c>
       <c r="J9">
-        <v>37.4374</v>
-      </c>
-      <c r="N9" t="str">
+        <v>527</v>
+      </c>
+      <c r="K9">
+        <v>33.566867</v>
+      </c>
+      <c r="L9">
+        <v>35.2352</v>
+      </c>
+      <c r="P9" t="str">
         <v>auto</v>
       </c>
-      <c r="O9" t="str">
+      <c r="Q9" t="str">
         <v>proposed</v>
       </c>
-      <c r="P9" t="str">
+      <c r="R9" t="str">
         <v>medium</v>
       </c>
-      <c r="Q9">
+      <c r="S9">
         <v>1</v>
       </c>
-      <c r="R9" t="str">
+      <c r="T9" t="str">
         <v>false</v>
       </c>
     </row>
@@ -1623,7 +2005,7 @@
         <v>e31e497a-d9c4-4ec0-b47f-531e3e5f83d8</v>
       </c>
       <c r="B10" t="str">
-        <v>d6b790ec-1c92-4ab4-80e4-fcd54adf69c1</v>
+        <v>43016980-1892-4da4-a53e-5905bf8ef55f</v>
       </c>
       <c r="C10" t="str">
         <v>investigation</v>
@@ -1638,31 +2020,37 @@
         <v>17</v>
       </c>
       <c r="G10">
-        <v>576</v>
+        <v>537</v>
       </c>
       <c r="H10">
-        <v>740</v>
+        <v>559</v>
       </c>
       <c r="I10">
-        <v>38.571867</v>
+        <v>538</v>
       </c>
       <c r="J10">
-        <v>49.4494</v>
-      </c>
-      <c r="N10" t="str">
+        <v>560</v>
+      </c>
+      <c r="K10">
+        <v>35.969267</v>
+      </c>
+      <c r="L10">
+        <v>37.4374</v>
+      </c>
+      <c r="P10" t="str">
         <v>auto</v>
       </c>
-      <c r="O10" t="str">
+      <c r="Q10" t="str">
         <v>proposed</v>
       </c>
-      <c r="P10" t="str">
-        <v>low</v>
-      </c>
-      <c r="Q10">
-        <v>2</v>
-      </c>
       <c r="R10" t="str">
-        <v>true</v>
+        <v>medium</v>
+      </c>
+      <c r="S10">
+        <v>1</v>
+      </c>
+      <c r="T10" t="str">
+        <v>false</v>
       </c>
     </row>
     <row r="11">
@@ -1670,13 +2058,13 @@
         <v>e31e497a-d9c4-4ec0-b47f-531e3e5f83d8</v>
       </c>
       <c r="B11" t="str">
-        <v>9d631383-66e0-4888-b10e-f9fb50ba63e3</v>
+        <v>d6b790ec-1c92-4ab4-80e4-fcd54adf69c1</v>
       </c>
       <c r="C11" t="str">
-        <v>escape_entry_uncertain</v>
+        <v>investigation</v>
       </c>
       <c r="D11" t="str">
-        <v>candidate_hole_entry_not_protocol_escape</v>
+        <v>investigation</v>
       </c>
       <c r="E11">
         <v>18</v>
@@ -1685,46 +2073,112 @@
         <v>17</v>
       </c>
       <c r="G11">
-        <v>621</v>
+        <v>576</v>
       </c>
       <c r="H11">
         <v>740</v>
       </c>
       <c r="I11">
+        <v>577</v>
+      </c>
+      <c r="J11">
+        <v>741</v>
+      </c>
+      <c r="K11">
+        <v>38.571867</v>
+      </c>
+      <c r="L11">
+        <v>49.4494</v>
+      </c>
+      <c r="P11" t="str">
+        <v>auto</v>
+      </c>
+      <c r="Q11" t="str">
+        <v>proposed</v>
+      </c>
+      <c r="R11" t="str">
+        <v>low</v>
+      </c>
+      <c r="S11">
+        <v>2</v>
+      </c>
+      <c r="T11" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>e31e497a-d9c4-4ec0-b47f-531e3e5f83d8</v>
+      </c>
+      <c r="B12" t="str">
+        <v>9d631383-66e0-4888-b10e-f9fb50ba63e3</v>
+      </c>
+      <c r="C12" t="str">
+        <v>escape_entry_uncertain</v>
+      </c>
+      <c r="D12" t="str">
+        <v>candidate_hole_entry_not_protocol_escape</v>
+      </c>
+      <c r="E12">
+        <v>18</v>
+      </c>
+      <c r="F12">
+        <v>17</v>
+      </c>
+      <c r="G12">
+        <v>621</v>
+      </c>
+      <c r="H12">
+        <v>740</v>
+      </c>
+      <c r="I12">
+        <v>622</v>
+      </c>
+      <c r="J12">
+        <v>741</v>
+      </c>
+      <c r="K12">
         <v>41.574867</v>
       </c>
-      <c r="J11">
+      <c r="L12">
         <v>49.4494</v>
       </c>
-      <c r="K11">
+      <c r="M12">
         <v>41.574867</v>
       </c>
-      <c r="M11">
+      <c r="O12">
         <v>49.4494</v>
       </c>
-      <c r="N11" t="str">
+      <c r="P12" t="str">
         <v>auto</v>
       </c>
-      <c r="O11" t="str">
+      <c r="Q12" t="str">
         <v>proposed</v>
       </c>
-      <c r="P11" t="str">
+      <c r="R12" t="str">
         <v>medium</v>
       </c>
-      <c r="T11">
+      <c r="V12">
         <v>3</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:X12"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:V11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:X12"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C42"/>
+  <cols>
+    <col min="1" max="1" width="22.83203125" customWidth="1"/>
+    <col min="2" max="2" width="36.83203125" customWidth="1"/>
+    <col min="3" max="3" width="48.83203125" customWidth="1"/>
+    <col min="4" max="4" width="48.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1745,7 +2199,7 @@
         <v>exportedAt</v>
       </c>
       <c r="C2" t="str">
-        <v>2026-09-07T19:54:09.007Z</v>
+        <v>2026-09-07T20:08:18.622Z</v>
       </c>
     </row>
     <row r="3">
@@ -2186,15 +2640,22 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C42"/>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C42"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F17"/>
+  <cols>
+    <col min="1" max="1" width="22.83203125" customWidth="1"/>
+    <col min="2" max="2" width="36.83203125" customWidth="1"/>
+    <col min="3" max="3" width="48.83203125" customWidth="1"/>
+    <col min="4" max="4" width="48.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2522,15 +2983,22 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:F17"/>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:F17"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:U2"/>
+  <cols>
+    <col min="1" max="1" width="22.83203125" customWidth="1"/>
+    <col min="2" max="2" width="36.83203125" customWidth="1"/>
+    <col min="3" max="3" width="48.83203125" customWidth="1"/>
+    <col min="4" max="4" width="48.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2651,6 +3119,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:U2"/>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:U2"/>
   </ignoredErrors>
